--- a/output/lettera36.xlsx
+++ b/output/lettera36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="125">
   <si>
     <t>word</t>
   </si>
@@ -25,9 +25,6 @@
     <t>lemma</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Molto</t>
   </si>
   <si>
@@ -43,9 +40,6 @@
     <t>osservandissimo</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Ho</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>veramente</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>eccellente</t>
   </si>
   <si>
@@ -115,9 +106,6 @@
     <t>casa</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Egli</t>
   </si>
   <si>
@@ -148,9 +136,6 @@
     <t>mi</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>per</t>
   </si>
   <si>
@@ -175,9 +160,6 @@
     <t>in</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>ogni</t>
   </si>
   <si>
@@ -202,9 +184,6 @@
     <t>che</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>me</t>
   </si>
   <si>
@@ -229,9 +208,6 @@
     <t>sicuro</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>appresso</t>
   </si>
   <si>
@@ -253,9 +229,6 @@
     <t>altro</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>lo</t>
   </si>
   <si>
@@ -283,9 +256,6 @@
     <t>sarà</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>il</t>
   </si>
   <si>
@@ -301,18 +271,12 @@
     <t>mani</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>pregarle</t>
   </si>
   <si>
     <t>felicità</t>
   </si>
   <si>
-    <t>ORD</t>
-  </si>
-  <si>
     <t>ADV</t>
   </si>
   <si>
@@ -325,9 +289,6 @@
     <t>PRO:poss</t>
   </si>
   <si>
-    <t>PON</t>
-  </si>
-  <si>
     <t>VER:pres</t>
   </si>
   <si>
@@ -346,9 +307,6 @@
     <t>CON</t>
   </si>
   <si>
-    <t>NUM</t>
-  </si>
-  <si>
     <t>PRO:rela</t>
   </si>
   <si>
@@ -374,9 +332,6 @@
   </si>
   <si>
     <t>PRO:demo</t>
-  </si>
-  <si>
-    <t>@card@</t>
   </si>
   <si>
     <t>signore</t>
@@ -791,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -810,10 +765,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -821,10 +776,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -832,10 +787,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -843,10 +798,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -854,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -865,10 +820,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -876,10 +831,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -887,10 +842,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -898,7 +853,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -909,10 +864,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -920,10 +875,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -931,10 +886,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -942,10 +897,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -953,7 +908,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -964,7 +919,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -975,7 +930,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -983,35 +938,35 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1019,10 +974,10 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1030,7 +985,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -1041,7 +996,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
@@ -1049,79 +1004,79 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1129,7 +1084,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
@@ -1140,10 +1095,10 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1151,10 +1106,10 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1162,10 +1117,10 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1176,7 +1131,7 @@
         <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1184,65 +1139,65 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1250,7 +1205,7 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
         <v>38</v>
@@ -1261,7 +1216,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
         <v>39</v>
@@ -1269,593 +1224,593 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
         <v>103</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B63" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C66" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C70" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B71" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B73" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C75" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C76" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B79" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C85" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C86" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C87" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C88" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C89" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C94" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B95" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B96" t="s">
         <v>103</v>
       </c>
       <c r="C96" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C97" t="s">
         <v>80</v>
@@ -1863,321 +1818,200 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C98" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B100" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C101" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C102" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C103" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="C104" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B105" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C106" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C107" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C108" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C109" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C110" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="C113" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C115" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>12</v>
-      </c>
-      <c r="B116" t="s">
-        <v>106</v>
-      </c>
-      <c r="C116" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
-        <v>94</v>
-      </c>
-      <c r="B117" t="s">
-        <v>101</v>
-      </c>
-      <c r="C117" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" t="s">
-        <v>31</v>
-      </c>
-      <c r="B118" t="s">
-        <v>107</v>
-      </c>
-      <c r="C118" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" t="s">
-        <v>14</v>
-      </c>
-      <c r="B119" t="s">
-        <v>102</v>
-      </c>
-      <c r="C119" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>101</v>
-      </c>
-      <c r="C120" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" t="s">
-        <v>16</v>
-      </c>
-      <c r="B121" t="s">
-        <v>100</v>
-      </c>
-      <c r="C121" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" t="s">
-        <v>19</v>
-      </c>
-      <c r="B122" t="s">
-        <v>109</v>
-      </c>
-      <c r="C122" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" t="s">
-        <v>20</v>
-      </c>
-      <c r="B123" t="s">
-        <v>107</v>
-      </c>
-      <c r="C123" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" t="s">
-        <v>95</v>
-      </c>
-      <c r="B124" t="s">
-        <v>103</v>
-      </c>
-      <c r="C124" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" t="s">
-        <v>96</v>
-      </c>
-      <c r="B125" t="s">
-        <v>117</v>
-      </c>
-      <c r="C125" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" t="s">
-        <v>97</v>
-      </c>
-      <c r="B126" t="s">
-        <v>101</v>
-      </c>
-      <c r="C126" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/output/lettera36.xlsx
+++ b/output/lettera36.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="152">
   <si>
     <t>word</t>
   </si>
@@ -25,370 +25,451 @@
     <t>lemma</t>
   </si>
   <si>
-    <t>Molto</t>
-  </si>
-  <si>
-    <t>Illustre</t>
-  </si>
-  <si>
-    <t>Signor</t>
+    <t>r</t>
+  </si>
+  <si>
+    <t>Sebene</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>era</t>
+  </si>
+  <si>
+    <t>necessario</t>
+  </si>
+  <si>
+    <t>ch’ella</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>rendesse</t>
+  </si>
+  <si>
+    <t>gratie</t>
+  </si>
+  <si>
+    <t>della</t>
+  </si>
+  <si>
+    <t>compagnia</t>
+  </si>
+  <si>
+    <t>d’archibusieri</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>cavallo</t>
+  </si>
+  <si>
+    <t>ch’io</t>
+  </si>
+  <si>
+    <t>ho</t>
+  </si>
+  <si>
+    <t>impiegato</t>
+  </si>
+  <si>
+    <t>nel</t>
+  </si>
+  <si>
+    <t>capitano</t>
+  </si>
+  <si>
+    <t>Biagio</t>
+  </si>
+  <si>
+    <t>suo</t>
+  </si>
+  <si>
+    <t>fratello</t>
+  </si>
+  <si>
+    <t>potendosi</t>
+  </si>
+  <si>
+    <t>ella</t>
+  </si>
+  <si>
+    <t>promettere</t>
+  </si>
+  <si>
+    <t>mia</t>
+  </si>
+  <si>
+    <t>buona</t>
+  </si>
+  <si>
+    <t>voluntà</t>
+  </si>
+  <si>
+    <t>per</t>
+  </si>
+  <si>
+    <t>lei</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>tutta</t>
+  </si>
+  <si>
+    <t>casa</t>
+  </si>
+  <si>
+    <t>sua</t>
+  </si>
+  <si>
+    <t>ogni</t>
+  </si>
+  <si>
+    <t>prontezza</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>avanzarla</t>
+  </si>
+  <si>
+    <t>proccurarle</t>
+  </si>
+  <si>
+    <t>beneficio</t>
+  </si>
+  <si>
+    <t>sodisfatione</t>
+  </si>
+  <si>
+    <t>è</t>
+  </si>
+  <si>
+    <t>però</t>
+  </si>
+  <si>
+    <t>stato</t>
+  </si>
+  <si>
+    <t>gratissimo</t>
+  </si>
+  <si>
+    <t>l’amorevole</t>
+  </si>
+  <si>
+    <t>testimonio</t>
+  </si>
+  <si>
+    <t>che</t>
+  </si>
+  <si>
+    <t>dà</t>
+  </si>
+  <si>
+    <t>giuntamente</t>
+  </si>
+  <si>
+    <t>continua</t>
+  </si>
+  <si>
+    <t>affetione</t>
+  </si>
+  <si>
+    <t>porta</t>
+  </si>
+  <si>
+    <t>alla</t>
+  </si>
+  <si>
+    <t>persona</t>
+  </si>
+  <si>
+    <t>assicurandola</t>
+  </si>
+  <si>
+    <t>l’occasione</t>
+  </si>
+  <si>
+    <t>gl’effetti</t>
+  </si>
+  <si>
+    <t>quel</t>
+  </si>
+  <si>
+    <t>sarà</t>
+  </si>
+  <si>
+    <t>mano</t>
+  </si>
+  <si>
+    <t>le</t>
+  </si>
+  <si>
+    <t>potranno</t>
+  </si>
+  <si>
+    <t>fare</t>
+  </si>
+  <si>
+    <t>conoscere</t>
+  </si>
+  <si>
+    <t>uguale</t>
+  </si>
+  <si>
+    <t>correspondentia</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>desiderio</t>
+  </si>
+  <si>
+    <t>tengo</t>
+  </si>
+  <si>
+    <t>di</t>
+  </si>
+  <si>
+    <t>giovarle</t>
+  </si>
+  <si>
+    <t>sempre</t>
+  </si>
+  <si>
+    <t>Con</t>
+  </si>
+  <si>
+    <t>me</t>
+  </si>
+  <si>
+    <t>offero</t>
+  </si>
+  <si>
+    <t>raccomando</t>
+  </si>
+  <si>
+    <t>prego</t>
+  </si>
+  <si>
+    <t>Nostro</t>
+  </si>
+  <si>
+    <t>Signore</t>
+  </si>
+  <si>
+    <t>la</t>
+  </si>
+  <si>
+    <t>conservi</t>
+  </si>
+  <si>
+    <t>Di</t>
+  </si>
+  <si>
+    <t>Liera</t>
+  </si>
+  <si>
+    <t>a’</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>giugno</t>
+  </si>
+  <si>
+    <t>Al</t>
+  </si>
+  <si>
+    <t>piacere</t>
+  </si>
+  <si>
+    <t>vostro</t>
+  </si>
+  <si>
+    <t>Alessandro</t>
+  </si>
+  <si>
+    <t>Farnese</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>Capozzuca</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>molto</t>
+  </si>
+  <si>
+    <t>Magnifico</t>
+  </si>
+  <si>
+    <t>il</t>
+  </si>
+  <si>
+    <t>signor</t>
+  </si>
+  <si>
+    <t>Capozucca</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>VER:impe</t>
+  </si>
+  <si>
+    <t>NOM</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t>VER:impf</t>
+  </si>
+  <si>
+    <t>ADJ</t>
+  </si>
+  <si>
+    <t>PRO:pers</t>
+  </si>
+  <si>
+    <t>VER:cimp</t>
+  </si>
+  <si>
+    <t>PRE:det</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>VER:pres</t>
+  </si>
+  <si>
+    <t>VER:pper</t>
+  </si>
+  <si>
+    <t>NPR</t>
+  </si>
+  <si>
+    <t>PRO:poss</t>
+  </si>
+  <si>
+    <t>VER:geru</t>
+  </si>
+  <si>
+    <t>VER:infi</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>PRO:rela</t>
+  </si>
+  <si>
+    <t>PRO:demo</t>
+  </si>
+  <si>
+    <t>VER:futu</t>
+  </si>
+  <si>
+    <t>DET:def</t>
+  </si>
+  <si>
+    <t>VER:cpre</t>
+  </si>
+  <si>
+    <t>NUM</t>
+  </si>
+  <si>
+    <t>essere</t>
+  </si>
+  <si>
+    <t>rendere</t>
+  </si>
+  <si>
+    <t>del</t>
+  </si>
+  <si>
+    <t>avere</t>
+  </si>
+  <si>
+    <t>impiegare</t>
+  </si>
+  <si>
+    <t>potere</t>
   </si>
   <si>
     <t>mio</t>
   </si>
   <si>
-    <t>osservandissimo</t>
-  </si>
-  <si>
-    <t>Ho</t>
-  </si>
-  <si>
-    <t>havuto</t>
-  </si>
-  <si>
-    <t>le</t>
-  </si>
-  <si>
-    <t>di</t>
-  </si>
-  <si>
-    <t>vostra</t>
-  </si>
-  <si>
-    <t>Signoria</t>
-  </si>
-  <si>
-    <t>illustre</t>
-  </si>
-  <si>
-    <t>col</t>
-  </si>
-  <si>
-    <t>disegno</t>
-  </si>
-  <si>
-    <t>e</t>
+    <t>buono</t>
+  </si>
+  <si>
+    <t>tutto</t>
+  </si>
+  <si>
+    <t>avanzare</t>
+  </si>
+  <si>
+    <t>essere|stare</t>
+  </si>
+  <si>
+    <t>grato</t>
+  </si>
+  <si>
+    <t>dare</t>
+  </si>
+  <si>
+    <t>continuo</t>
+  </si>
+  <si>
+    <t>portare</t>
+  </si>
+  <si>
+    <t>assicurare</t>
+  </si>
+  <si>
+    <t>quello</t>
+  </si>
+  <si>
+    <t>tenere</t>
+  </si>
+  <si>
+    <t>giovare</t>
   </si>
   <si>
     <t>con</t>
   </si>
   <si>
-    <t>direttive</t>
-  </si>
-  <si>
-    <t>al</t>
-  </si>
-  <si>
-    <t>veramente</t>
-  </si>
-  <si>
-    <t>eccellente</t>
-  </si>
-  <si>
-    <t>Paladio</t>
-  </si>
-  <si>
-    <t>quali</t>
-  </si>
-  <si>
-    <t>li</t>
-  </si>
-  <si>
-    <t>mandai</t>
-  </si>
-  <si>
-    <t>subito</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>casa</t>
-  </si>
-  <si>
-    <t>Egli</t>
-  </si>
-  <si>
-    <t>sia</t>
-  </si>
-  <si>
-    <t>trovava</t>
-  </si>
-  <si>
-    <t>fuori</t>
-  </si>
-  <si>
-    <t>Vicenza</t>
-  </si>
-  <si>
-    <t>quindi</t>
-  </si>
-  <si>
-    <t>è</t>
-  </si>
-  <si>
-    <t>ritornato</t>
-  </si>
-  <si>
-    <t>non</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>per</t>
-  </si>
-  <si>
-    <t>ancora</t>
-  </si>
-  <si>
-    <t>successo</t>
-  </si>
-  <si>
-    <t>vederlo</t>
-  </si>
-  <si>
-    <t>ma</t>
-  </si>
-  <si>
-    <t>mancarò</t>
-  </si>
-  <si>
-    <t>trovarlo</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>ogni</t>
-  </si>
-  <si>
-    <t>modo</t>
-  </si>
-  <si>
-    <t>far</t>
-  </si>
-  <si>
-    <t>esso</t>
-  </si>
-  <si>
-    <t>lui</t>
-  </si>
-  <si>
-    <t>bocca</t>
-  </si>
-  <si>
-    <t>l’ufficio</t>
-  </si>
-  <si>
-    <t>che</t>
-  </si>
-  <si>
-    <t>me</t>
-  </si>
-  <si>
-    <t>impone</t>
-  </si>
-  <si>
-    <t>Avenga</t>
-  </si>
-  <si>
-    <t>havendogli</t>
-  </si>
-  <si>
-    <t>essa</t>
-  </si>
-  <si>
-    <t>scritto</t>
-  </si>
-  <si>
-    <t>son</t>
-  </si>
-  <si>
-    <t>sicuro</t>
-  </si>
-  <si>
-    <t>appresso</t>
-  </si>
-  <si>
-    <t>così</t>
-  </si>
-  <si>
-    <t>bel</t>
-  </si>
-  <si>
-    <t>spirto</t>
-  </si>
-  <si>
-    <t>superfluo</t>
-  </si>
-  <si>
-    <t>aggiugner</t>
-  </si>
-  <si>
-    <t>altro</t>
-  </si>
-  <si>
-    <t>lo</t>
-  </si>
-  <si>
-    <t>farò</t>
-  </si>
-  <si>
-    <t>ubbedir</t>
-  </si>
-  <si>
-    <t>lei</t>
-  </si>
-  <si>
-    <t>molto</t>
-  </si>
-  <si>
-    <t>disidero</t>
-  </si>
-  <si>
-    <t>servire</t>
-  </si>
-  <si>
-    <t>Il</t>
-  </si>
-  <si>
-    <t>sarà</t>
-  </si>
-  <si>
-    <t>il</t>
-  </si>
-  <si>
-    <t>fine</t>
-  </si>
-  <si>
-    <t>questa</t>
-  </si>
-  <si>
-    <t>basciar</t>
-  </si>
-  <si>
-    <t>mani</t>
-  </si>
-  <si>
-    <t>pregarle</t>
-  </si>
-  <si>
-    <t>felicità</t>
-  </si>
-  <si>
-    <t>ADV</t>
-  </si>
-  <si>
-    <t>ADJ</t>
-  </si>
-  <si>
-    <t>NOM</t>
-  </si>
-  <si>
-    <t>PRO:poss</t>
-  </si>
-  <si>
-    <t>VER:pres</t>
-  </si>
-  <si>
-    <t>VER:pper</t>
-  </si>
-  <si>
-    <t>DET:def</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>PRE:det</t>
-  </si>
-  <si>
-    <t>CON</t>
-  </si>
-  <si>
-    <t>PRO:rela</t>
-  </si>
-  <si>
-    <t>PRO:pers</t>
-  </si>
-  <si>
-    <t>VER:remo</t>
-  </si>
-  <si>
-    <t>VER:cpre</t>
-  </si>
-  <si>
-    <t>VER:impf</t>
-  </si>
-  <si>
-    <t>NPR</t>
-  </si>
-  <si>
-    <t>VER:infi</t>
-  </si>
-  <si>
-    <t>VER:futu</t>
-  </si>
-  <si>
-    <t>PRO:demo</t>
+    <t>raccomandare</t>
+  </si>
+  <si>
+    <t>nostro</t>
+  </si>
+  <si>
+    <t>signora|signore</t>
+  </si>
+  <si>
+    <t>conservare</t>
+  </si>
+  <si>
+    <t>magnifico</t>
   </si>
   <si>
     <t>signore</t>
-  </si>
-  <si>
-    <t>avere</t>
-  </si>
-  <si>
-    <t>vostro</t>
-  </si>
-  <si>
-    <t>signoria</t>
-  </si>
-  <si>
-    <t>direttiva</t>
-  </si>
-  <si>
-    <t>quale</t>
-  </si>
-  <si>
-    <t>mandare</t>
-  </si>
-  <si>
-    <t>egli</t>
-  </si>
-  <si>
-    <t>essere</t>
-  </si>
-  <si>
-    <t>trovare</t>
-  </si>
-  <si>
-    <t>ritornare</t>
-  </si>
-  <si>
-    <t>succedere</t>
-  </si>
-  <si>
-    <t>vedere</t>
-  </si>
-  <si>
-    <t>fare</t>
-  </si>
-  <si>
-    <t>imporre</t>
-  </si>
-  <si>
-    <t>scrivere</t>
-  </si>
-  <si>
-    <t>questo</t>
-  </si>
-  <si>
-    <t>mano</t>
-  </si>
-  <si>
-    <t>pregare</t>
   </si>
 </sst>
 </file>
@@ -746,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -765,10 +846,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -776,10 +857,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -787,10 +868,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -798,10 +879,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -809,7 +890,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -820,10 +901,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -831,7 +912,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -842,10 +923,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -853,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -864,10 +945,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -875,10 +956,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -886,7 +967,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -897,7 +978,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -908,7 +989,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -919,7 +1000,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -930,186 +1011,186 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1117,494 +1198,494 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C58" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="C73" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B76" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1612,7 +1693,7 @@
         <v>64</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s">
         <v>64</v>
@@ -1623,10 +1704,10 @@
         <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1634,7 +1715,7 @@
         <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C81" t="s">
         <v>66</v>
@@ -1645,7 +1726,7 @@
         <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C82" t="s">
         <v>67</v>
@@ -1653,189 +1734,189 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B89" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C90" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B91" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C91" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C92" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B94" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C95" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B96" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C97" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C98" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1843,7 +1924,7 @@
         <v>80</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C100" t="s">
         <v>80</v>
@@ -1854,164 +1935,329 @@
         <v>81</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C101" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="B102" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C102" t="s">
-        <v>11</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="B104" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C106" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B107" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="B108" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="B109" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B110" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C110" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="B111" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="B113" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C113" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B114" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C114" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B115" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>86</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>94</v>
+      </c>
+      <c r="B116" t="s">
+        <v>105</v>
+      </c>
+      <c r="C116" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>112</v>
+      </c>
+      <c r="C117" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>95</v>
+      </c>
+      <c r="B118" t="s">
+        <v>115</v>
+      </c>
+      <c r="C118" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>96</v>
+      </c>
+      <c r="B119" t="s">
+        <v>105</v>
+      </c>
+      <c r="C119" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>97</v>
+      </c>
+      <c r="B120" t="s">
+        <v>117</v>
+      </c>
+      <c r="C120" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>90</v>
+      </c>
+      <c r="B121" t="s">
+        <v>115</v>
+      </c>
+      <c r="C121" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>98</v>
+      </c>
+      <c r="B122" t="s">
+        <v>106</v>
+      </c>
+      <c r="C122" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>99</v>
+      </c>
+      <c r="B123" t="s">
+        <v>108</v>
+      </c>
+      <c r="C123" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>82</v>
+      </c>
+      <c r="B124" t="s">
+        <v>105</v>
+      </c>
+      <c r="C124" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>100</v>
+      </c>
+      <c r="B125" t="s">
+        <v>123</v>
+      </c>
+      <c r="C125" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>101</v>
+      </c>
+      <c r="B126" t="s">
+        <v>105</v>
+      </c>
+      <c r="C126" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>95</v>
+      </c>
+      <c r="B127" t="s">
+        <v>115</v>
+      </c>
+      <c r="C127" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>102</v>
+      </c>
+      <c r="B128" t="s">
+        <v>105</v>
+      </c>
+      <c r="C128" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>112</v>
+      </c>
+      <c r="C129" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>103</v>
+      </c>
+      <c r="B130" t="s">
+        <v>115</v>
+      </c>
+      <c r="C130" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
